--- a/games/AFA_Handball_vs_Denver_2026-08-22.xlsx
+++ b/games/AFA_Handball_vs_Denver_2026-08-22.xlsx
@@ -404,10 +404,6 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B17"/>
-  <cols>
-    <col min="1" max="1" width="26.83203125" customWidth="1"/>
-    <col min="2" max="2" width="34.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -552,26 +548,6 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:R16"/>
-  <cols>
-    <col min="1" max="1" width="5.83203125" customWidth="1"/>
-    <col min="2" max="2" width="18.83203125" customWidth="1"/>
-    <col min="3" max="3" width="5.83203125" customWidth="1"/>
-    <col min="4" max="4" width="9.83203125" customWidth="1"/>
-    <col min="5" max="5" width="9.83203125" customWidth="1"/>
-    <col min="6" max="6" width="9.83203125" customWidth="1"/>
-    <col min="7" max="7" width="9.83203125" customWidth="1"/>
-    <col min="8" max="8" width="9.83203125" customWidth="1"/>
-    <col min="9" max="9" width="9.83203125" customWidth="1"/>
-    <col min="10" max="10" width="9.83203125" customWidth="1"/>
-    <col min="11" max="11" width="9.83203125" customWidth="1"/>
-    <col min="12" max="12" width="9.83203125" customWidth="1"/>
-    <col min="13" max="13" width="9.83203125" customWidth="1"/>
-    <col min="14" max="14" width="9.83203125" customWidth="1"/>
-    <col min="15" max="15" width="9.83203125" customWidth="1"/>
-    <col min="16" max="16" width="9.83203125" customWidth="1"/>
-    <col min="17" max="17" width="9.83203125" customWidth="1"/>
-    <col min="18" max="18" width="9.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1478,18 +1454,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I4"/>
-  <cols>
-    <col min="1" max="1" width="5.83203125" customWidth="1"/>
-    <col min="2" max="2" width="22.83203125" customWidth="1"/>
-    <col min="3" max="3" width="12.83203125" customWidth="1"/>
-    <col min="4" max="4" width="12.83203125" customWidth="1"/>
-    <col min="5" max="5" width="12.83203125" customWidth="1"/>
-    <col min="6" max="6" width="12.83203125" customWidth="1"/>
-    <col min="7" max="7" width="12.83203125" customWidth="1"/>
-    <col min="8" max="8" width="12.83203125" customWidth="1"/>
-    <col min="9" max="9" width="12.83203125" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:I3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1551,65 +1516,36 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="B3" t="str">
-        <v>C3C Ian P. Cavendish</v>
+        <v>C1C Zachary D. Crane</v>
       </c>
       <c r="C3">
+        <v>41</v>
+      </c>
+      <c r="D3">
+        <v>8</v>
+      </c>
+      <c r="E3">
+        <v>26.7</v>
+      </c>
+      <c r="F3">
+        <v>22</v>
+      </c>
+      <c r="G3">
         <v>1</v>
       </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>100</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
       <c r="H3">
         <v>0</v>
       </c>
       <c r="I3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4">
-        <v>4</v>
-      </c>
-      <c r="B4" t="str">
-        <v>C1C Zachary D. Crane</v>
-      </c>
-      <c r="C4">
-        <v>41</v>
-      </c>
-      <c r="D4">
-        <v>8</v>
-      </c>
-      <c r="E4">
-        <v>26.7</v>
-      </c>
-      <c r="F4">
-        <v>22</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I3"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1617,11 +1553,6 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C12"/>
-  <cols>
-    <col min="1" max="1" width="24.83203125" customWidth="1"/>
-    <col min="2" max="2" width="12.83203125" customWidth="1"/>
-    <col min="3" max="3" width="16.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1765,19 +1696,6 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:K155"/>
-  <cols>
-    <col min="1" max="1" width="4.83203125" customWidth="1"/>
-    <col min="2" max="2" width="5.83203125" customWidth="1"/>
-    <col min="3" max="3" width="7.83203125" customWidth="1"/>
-    <col min="4" max="4" width="14.83203125" customWidth="1"/>
-    <col min="5" max="5" width="4.83203125" customWidth="1"/>
-    <col min="6" max="6" width="14.83203125" customWidth="1"/>
-    <col min="7" max="7" width="26.83203125" customWidth="1"/>
-    <col min="8" max="8" width="22.83203125" customWidth="1"/>
-    <col min="9" max="9" width="7.83203125" customWidth="1"/>
-    <col min="10" max="10" width="8.83203125" customWidth="1"/>
-    <col min="11" max="11" width="8.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -7214,19 +7132,6 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:K64"/>
-  <cols>
-    <col min="1" max="1" width="4.83203125" customWidth="1"/>
-    <col min="2" max="2" width="5.83203125" customWidth="1"/>
-    <col min="3" max="3" width="7.83203125" customWidth="1"/>
-    <col min="4" max="4" width="14.83203125" customWidth="1"/>
-    <col min="5" max="5" width="4.83203125" customWidth="1"/>
-    <col min="6" max="6" width="14.83203125" customWidth="1"/>
-    <col min="7" max="7" width="8.83203125" customWidth="1"/>
-    <col min="8" max="8" width="5.83203125" customWidth="1"/>
-    <col min="9" max="9" width="7.83203125" customWidth="1"/>
-    <col min="10" max="10" width="7.83203125" customWidth="1"/>
-    <col min="11" max="11" width="40.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -9478,13 +9383,6 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E15"/>
-  <cols>
-    <col min="1" max="1" width="5.83203125" customWidth="1"/>
-    <col min="2" max="2" width="18.83203125" customWidth="1"/>
-    <col min="3" max="3" width="6.83203125" customWidth="1"/>
-    <col min="4" max="4" width="8.83203125" customWidth="1"/>
-    <col min="5" max="5" width="8.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
